--- a/tests/TC-04/results/unscheduled_courses_even.xlsx
+++ b/tests/TC-04/results/unscheduled_courses_even.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS405</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Could not place combined LAB</t>
+          <t>Could not place combined LEC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS406</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -512,19 +512,19 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Could not place combined LAB</t>
+          <t>Could not place combined LEC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DA151</t>
+          <t>CS407</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -543,6 +543,206 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Could not place combined LEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CS408</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CS409</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CS410</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CS411</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CS412</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>LEC, TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CS413</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>LEC, TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CS414</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>LEC, TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CS415</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>LEC, TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
         </is>
       </c>
     </row>

--- a/tests/TC-04/results/unscheduled_courses_even.xlsx
+++ b/tests/TC-04/results/unscheduled_courses_even.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CS405</t>
+          <t>CS407</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CS406</t>
+          <t>CS408</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CS407</t>
+          <t>CS409</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CS408</t>
+          <t>CS410</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CS409</t>
+          <t>CS411</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CS410</t>
+          <t>CS412</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -612,19 +612,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LEC, TUT</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Could not place combined LEC</t>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CS411</t>
+          <t>CS413</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LEC, TUT</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Could not place combined LEC</t>
+          <t>Could not place combined LEC; Could not place combined TUT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CS412</t>
+          <t>CS414</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CS413</t>
+          <t>CS415</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -691,56 +691,6 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Could not place combined LEC; Could not place combined TUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CS414</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CSE</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>LEC, TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Could not place combined LEC; Could not place combined TUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CS415</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>CSE</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>LEC, TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Could not place combined LEC; Could not place combined TUT</t>
         </is>
